--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200qsp_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200qsp_incorrect.xlsx
@@ -473,9 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,9 +498,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -527,9 +523,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -554,9 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -581,9 +573,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -608,9 +598,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -660,9 +648,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -687,9 +673,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -714,8 +698,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raltegravir, Elvitegravir, Dolutegravir
-```</t>
+          <t>Raltegravir, Elvitegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -740,9 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IN
-```
-```</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -767,9 +748,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -794,9 +773,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PI, INSTI, NNRTI
-```
-```</t>
+          <t>PI, INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -821,8 +798,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DTG, RAL, EFV, ETR
-```</t>
+          <t>DTG, RAL, EFV, ETR</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -847,9 +823,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -874,9 +848,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -926,9 +898,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -953,9 +923,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1005,9 +973,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1032,9 +998,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Senegal
-```
-```</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1084,9 +1048,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1136,9 +1098,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27
-```
-```</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1163,9 +1123,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI
-```
-```</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1190,9 +1148,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1242,9 +1198,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1269,9 +1223,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1296,9 +1248,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1348,9 +1298,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1375,9 +1323,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1402,9 +1348,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1429,9 +1373,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI
-```
-```</t>
+          <t>NRTI,NNRTI,PI</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1456,8 +1398,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TDF,3TC,FTC,EVG
-```</t>
+          <t>TDF,3TC,FTC,EVG</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1507,9 +1448,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1534,9 +1473,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1561,9 +1498,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Supernatant
-```
-```</t>
+          <t>Supernatant</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1588,9 +1523,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NRTI
-```
-```</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1615,8 +1548,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tenofovir, emtricitabine, lamivudine, zidovudine
-```</t>
+          <t>Tenofovir, emtricitabine, lamivudine, zidovudine</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1641,9 +1573,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lesotho
-```
-```</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1668,9 +1598,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2020
-```
-```</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1695,9 +1623,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1722,8 +1648,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1748,9 +1673,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1775,9 +1698,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1802,9 +1723,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1829,9 +1748,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>35
-```
-```</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1856,9 +1773,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1883,9 +1798,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1910,9 +1823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI
-```
-```</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1937,9 +1848,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1989,8 +1898,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZDV, 3TC, LPV/r, EFV, NVP, TDF, ABC, DRV, RAL, DTG, BIC
-```</t>
+          <t>ZDV, 3TC, LPV/r, EFV, NVP, TDF, ABC, DRV, RAL, DTG, BIC</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2015,9 +1923,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2067,9 +1973,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>171
-```
-```</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2094,9 +1998,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>South Africa, Zimbabwe, Malawi, Mozambique
-```
-```</t>
+          <t>South Africa, Zimbabwe, Malawi, Mozambique</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2121,9 +2023,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2022
-```
-```</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2148,9 +2048,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RT
-```
-```</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2175,9 +2073,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2202,9 +2098,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2229,9 +2123,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2256,8 +2148,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TAF, FTC, TDF, 3TC, DTG, EFV
-```</t>
+          <t>TAF, FTC, TDF, 3TC, DTG, EFV</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2307,9 +2198,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2334,9 +2223,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2386,8 +2273,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FTC, TDF, ATV/r, RAL
-```</t>
+          <t>FTC, TDF, ATV/r, RAL</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2412,9 +2298,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2464,9 +2348,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020–2021
-```
-```</t>
+          <t>2020–2021</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2491,9 +2373,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2518,9 +2398,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2545,9 +2423,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2572,9 +2448,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2599,9 +2473,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2626,9 +2498,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2653,8 +2523,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2704,9 +2573,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2731,9 +2598,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2758,9 +2623,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>INSTI, NRTI
-```
-```</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2810,9 +2673,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2837,9 +2698,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2864,8 +2723,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2915,9 +2773,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>50
-```
-```</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2942,9 +2798,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2969,9 +2823,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -3021,9 +2873,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3098,9 +2948,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3125,8 +2973,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3151,9 +2998,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Botswana, Eswatini, Lesotho, Malawi, Tanzania, Uganda
-```
-```</t>
+          <t>Botswana, Eswatini, Lesotho, Malawi, Tanzania, Uganda</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3178,9 +3023,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2017-2020
-```
-```</t>
+          <t>2017-2020</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3230,9 +3073,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3257,9 +3098,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3309,9 +3148,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3361,9 +3198,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2008-2022
-```
-```</t>
+          <t>2008-2022</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3388,9 +3223,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3415,9 +3248,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3442,8 +3273,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3493,9 +3323,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3520,9 +3348,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PR, RT, IN
-```
-```</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3622,9 +3448,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>56
-```
-```</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3649,9 +3473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Env
-```
-```</t>
+          <t>PR, RT, IN, Env</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3701,8 +3523,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Rilpivirine, Darunavir, Ritonavir
-```</t>
+          <t>Rilpivirine, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3727,9 +3548,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2014–2020
-```
-```</t>
+          <t>2014–2020</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3754,9 +3573,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3806,9 +3623,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>IN
-```
-```</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3883,9 +3698,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3910,9 +3723,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3937,9 +3748,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PBMC, Plasma
-```
-```</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3989,9 +3798,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4041,9 +3848,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Both
-```
-```</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -4118,9 +3923,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Whole blood
-```
-```</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -4170,9 +3973,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -4197,9 +3998,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4224,9 +4023,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4251,9 +4048,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Not applicable
-```
-```</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4278,9 +4073,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI
-```
-```</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4330,9 +4123,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Whole blood
-```
-```</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4357,9 +4148,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -4409,9 +4198,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4461,9 +4248,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15369
-```
-```</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4488,9 +4273,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4515,9 +4298,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NRTI, PI
-```
-```</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4567,8 +4348,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TDF, 3TC, ABC, EFV, DTG
-```</t>
+          <t>TDF, 3TC, ABC, EFV, DTG</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4618,9 +4398,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env
-```
-```</t>
+          <t>Gag, Pol, Env</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4645,9 +4423,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4672,9 +4448,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4699,9 +4473,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4726,8 +4498,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4777,9 +4548,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4854,9 +4623,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>None
-```
-```</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4881,8 +4648,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>None
-```</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4932,9 +4698,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4959,9 +4723,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4986,9 +4748,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Iran
-```
-```</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -5013,9 +4773,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2019-2020
-```
-```</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -5040,9 +4798,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -5067,9 +4823,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI
-```
-```</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -5094,9 +4848,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -5121,9 +4873,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -5148,9 +4898,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -5175,9 +4923,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -5202,9 +4948,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -5229,8 +4973,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -5255,9 +4998,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -5307,9 +5048,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5334,9 +5073,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5361,9 +5098,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5388,9 +5123,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5415,8 +5148,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Etravirine, dolutegravir, darunavir, ritonavir
-```</t>
+          <t>Etravirine, dolutegravir, darunavir, ritonavir</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5491,9 +5223,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0
-```
-```</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5518,9 +5248,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5545,9 +5273,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5572,9 +5298,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5599,8 +5323,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5650,9 +5373,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5677,9 +5398,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5704,9 +5423,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5756,9 +5473,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5808,9 +5523,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>208
-```
-```</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5860,8 +5573,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Not reported
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5886,9 +5598,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>197
-```
-```</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5913,9 +5623,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Italy
-```
-```</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5940,9 +5648,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2019–2022
-```
-```</t>
+          <t>2019–2022</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5967,9 +5673,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5994,9 +5698,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -6021,9 +5723,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -6073,9 +5773,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>793902
-```
-```</t>
+          <t>793902</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -6100,9 +5798,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kenya
-```
-```</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -6127,9 +5823,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2015–2021
-```
-```</t>
+          <t>2015–2021</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -6154,9 +5848,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -6181,9 +5873,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -6208,9 +5898,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -6235,9 +5923,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -6312,9 +5998,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6339,9 +6023,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6366,9 +6048,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6393,9 +6073,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6420,8 +6098,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir Alafenamide (TAF), Darunavir (DRV), Dolutegravir (DTG), Elvitegravir (EVG)
-```</t>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir Alafenamide (TAF), Darunavir (DRV), Dolutegravir (DTG), Elvitegravir (EVG)</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6446,9 +6123,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6498,9 +6173,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6525,9 +6198,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6552,9 +6223,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6579,8 +6248,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG
-```</t>
+          <t>TDF, 3TC, DTG</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6630,9 +6298,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6657,9 +6323,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6684,9 +6348,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI PI, INSTI</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6711,8 +6373,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>FTC, TDF, EFV, ATV/r, DTG
-```</t>
+          <t>FTC, TDF, EFV, ATV/r, DTG</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6762,9 +6423,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6814,9 +6473,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Env
-```
-```</t>
+          <t>Env</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6841,9 +6498,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6868,9 +6523,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6920,9 +6573,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6997,9 +6648,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI
-```
-```</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -7049,9 +6698,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -7101,9 +6748,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4436
-```
-```</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -7128,9 +6773,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Ghana
-```
-```</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -7155,9 +6798,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2013-2022
-```
-```</t>
+          <t>2013-2022</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -7207,9 +6848,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -7234,9 +6873,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NGS
-```
-```</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -7311,9 +6948,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>75
-```
-```</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -7338,9 +6973,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RT
-```
-```</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -7365,9 +6998,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -7467,9 +7098,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7494,9 +7123,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Pol, Env
-```
-```</t>
+          <t>Pol, Env</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7521,9 +7148,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7548,9 +7173,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Pip&gt;tenofKO.&lt;
-```
-```</t>
+          <t>Pip&gt;tenofKO.&lt;</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7575,9 +7198,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7602,9 +7223,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>INSTIs, NNRTIs
-```
-```</t>
+          <t>INSTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7629,8 +7248,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Cabotegravir, Rilpivirine
-```</t>
+          <t>Cabotegravir, Rilpivirine</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -7655,9 +7273,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7707,9 +7323,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7759,9 +7373,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -7811,9 +7423,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Not reported
-```
-```</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7863,9 +7473,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>30
-```
-```</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -7890,9 +7498,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7917,9 +7523,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -7969,9 +7573,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1958
-```
-```</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -7996,9 +7598,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>PR, RT
-```
-```</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -8048,9 +7648,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Sanger sequencing
-```
-```</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -8075,8 +7673,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>TDF, AZT, 3TC, FTC, ABC, D4T, EFV, NVP, RPV, LPV/r, ATV/r, DRV/r
-```</t>
+          <t>TDF, AZT, 3TC, FTC, ABC, D4T, EFV, NVP, RPV, LPV/r, ATV/r, DRV/r</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -8101,9 +7698,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Sierra Leone
-```
-```</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -8128,9 +7723,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2022-2023
-```
-```</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -8155,9 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Plasma
-```
-```</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -8182,9 +7773,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -8209,9 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -8236,8 +7823,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir
-```</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -8262,9 +7848,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -8314,9 +7898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2015–2019
-```
-```</t>
+          <t>2015–2019</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -8341,9 +7923,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -8368,9 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI
-```
-```</t>
+          <t>NRTI,NNRTI,PI</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -8395,8 +7973,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NVP,NVP, cotrimoxazole, isoniazid
-```</t>
+          <t>NVP,NVP, cotrimoxazole, isoniazid</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -8446,9 +8023,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Dried Blood Spot (DBS)
-```
-```</t>
+          <t>Dried Blood Spot (DBS)</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -8473,8 +8048,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>3TC, ABC, LPV/r, TDF, FTC, RPV, DRV
-```</t>
+          <t>3TC, ABC, LPV/r, TDF, FTC, RPV, DRV</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -8549,9 +8123,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1040
-```
-```</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8626,9 +8198,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -8678,9 +8248,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2013-2023
-```
-```</t>
+          <t>2013-2023</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8705,9 +8273,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>IN
-```
-```</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8732,9 +8298,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8759,9 +8323,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -8786,9 +8348,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NRTI, INSTI
-```
-```</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8813,8 +8373,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DTG
-```</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8839,9 +8398,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8891,9 +8448,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1214
-```
-```</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8918,9 +8473,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>South Africa
-```
-```</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8945,9 +8498,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2019–2020
-```
-```</t>
+          <t>2019–2020</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8972,9 +8523,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8999,9 +8548,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -9026,9 +8573,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI
-```
-```</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -9053,8 +8598,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>TDF, 3TC, XTC, EFV, NVP, AZT, LPV/r, DTG
-```</t>
+          <t>TDF, 3TC, XTC, EFV, NVP, AZT, LPV/r, DTG</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -9104,9 +8648,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI
-```
-```</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -9156,9 +8698,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>195
-```
-```</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -9183,9 +8723,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Yes
-```
-```</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -9210,9 +8748,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI
-```
-```</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -9237,8 +8773,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, TenofovirDF or Abacavir
-```</t>
+          <t>EFV, NVP, AZT, 3TC, TenofovirDF or Abacavir</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -9263,9 +8798,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>No
-```
-```</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E335" t="n">

--- a/eval/learning-curve/results/learning_curve_gpt-4o_ft200qsp_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_gpt-4o_ft200qsp_incorrect.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -638,17 +638,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Raltegravir, Elvitegravir, Dolutegravir</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raltegravir, Elvitegravir, Dolutegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>PI, INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -763,7 +763,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PI, INSTI, NNRTI</t>
+          <t>DTG, RAL, EFV, ETR</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -788,17 +788,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DTG, RAL, EFV, ETR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -863,17 +863,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KU761565</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -888,17 +888,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -913,12 +913,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>KU761565</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1088,17 +1088,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MW484894, MW484895, MW484893, DQ380549, AF492618, MW48492</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada, Ethiopia</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NRTI,NNRTI,PI</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TDF,3TC,FTC,EVG</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>MW484894, MW484895, MW484893, DQ380549, AF492618, MW48492</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Canada, Ethiopia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TDF,3TC,FTC,EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OK263149 to OK263162</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Supernatant</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Supernatant</t>
+          <t>Tenofovir, emtricitabine, lamivudine, zidovudine</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>OK263149 to OK263162</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tenofovir, emtricitabine, lamivudine, zidovudine</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1588,17 +1588,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1738,17 +1738,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>ZDV, 3TC, LPV/r, EFV, NVP, TDF, ABC, DRV, RAL, DTG, BIC</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OM201778 - OM201846</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+          <t>OM201778 - OM201846</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZDV, 3TC, LPV/r, EFV, NVP, TDF, ABC, DRV, RAL, DTG, BIC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>South Africa, Zimbabwe, Malawi, Mozambique</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>TAF, FTC, TDF, 3TC, DTG, EFV</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>South Africa, Zimbabwe, Malawi, Mozambique</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TAF, FTC, TDF, 3TC, DTG, EFV</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2188,17 +2188,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>FTC, TDF, ATV/r, RAL</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2263,17 +2263,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FTC, TDF, ATV/r, RAL</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2288,17 +2288,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2020–2021</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>2020–2021</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2463,17 +2463,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2738,17 +2738,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>62 or 3</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3163,17 +3163,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2008-2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3213,17 +3213,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2008-2022</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RAL, DRV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rilpivirine, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>RAL, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Rilpivirine, Darunavir, Ritonavir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Whole Blood, Semen</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3713,17 +3713,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3838,17 +3838,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MW947591–MW957968, OP058117–OP058658</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>MW947591–MW957968, OP058117–OP058658</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3988,17 +3988,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4038,17 +4038,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -4063,17 +4063,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma; PBMC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4213,17 +4213,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4288,17 +4288,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NRTI, PI</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4313,17 +4313,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TDF, 3TC, ABC, EFV, DTG</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TDF, 3TC, ABC, EFV, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4363,17 +4363,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4388,17 +4388,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Gag, Pol, Env</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4588,17 +4588,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>OQ627458-OQ627474</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>OQ627458-OQ627474</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4663,17 +4663,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4788,17 +4788,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4988,17 +4988,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>OQ886077 - OQ888150</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>OQ886077 - OQ888150</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Etravirine, dolutegravir, darunavir, ritonavir</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Etravirine, dolutegravir, darunavir, ritonavir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5263,17 +5263,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5288,17 +5288,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5463,17 +5463,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5538,17 +5538,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MK580543-MK580618; JF273935-JF273965; JQ796152-JQ796169; MK867721-MK867755; OQ985493-OQ985958</t>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+          <t>MK580543-MK580618; JF273935-JF273965; JQ796152-JQ796169; MK867721-MK867755; OQ985493-OQ985958</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2019–2022</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>2019–2022</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>793902</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2015–2021</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>793902</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5863,17 +5863,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2015–2021</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir Alafenamide (TAF), Darunavir (DRV), Dolutegravir (DTG), Elvitegravir (EVG)</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6013,17 +6013,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6063,17 +6063,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6088,17 +6088,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir Alafenamide (TAF), Darunavir (DRV), Dolutegravir (DTG), Elvitegravir (EVG)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6188,17 +6188,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>TDF, 3TC, DTG</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6288,17 +6288,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI PI, INSTI</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>FTC, TDF, EFV, ATV/r, DTG</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6363,17 +6363,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>FTC, TDF, EFV, ATV/r, DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>OQ215322-OQ215382</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>OQ215322-OQ215382</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6838,17 +6838,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -6863,17 +6863,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -6938,17 +6938,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6963,17 +6963,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -7063,17 +7063,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pip&gt;tenofKO.&lt;</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Pol, Env</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>NRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DTG, DRV, TFV, FTC </t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Pip&gt;tenofKO.&lt;</t>
+          <t>Pol, Env</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7313,17 +7313,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7388,17 +7388,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -7413,17 +7413,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF, AZT, 3TC, FTC, ABC, D4T, EFV, NVP, RPV, LPV/r, ATV/r, DRV/r</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>TDF, AZT, 3TC, FTC, ABC, D4T, EFV, NVP, RPV, LPV/r, ATV/r, DRV/r</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -7713,17 +7713,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7763,17 +7763,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2015–2019</t>
+          <t>NRTI,NNRTI,PI</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -7913,17 +7913,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NVP,NVP, cotrimoxazole, isoniazid</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NRTI,NNRTI,PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NVP,NVP, cotrimoxazole, isoniazid</t>
+          <t>2015–2019</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dried Blood Spot (DBS)</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -8013,17 +8013,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Dried Blood Spot (DBS)</t>
+          <t>3TC, ABC, LPV/r, TDF, FTC, RPV, DRV</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3TC, ABC, LPV, AZT, DTG, FTC, TDF, DRV, EFV, NVP</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>3TC, ABC, LPV/r, TDF, FTC, RPV, DRV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2013-2023</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2013-2023</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8438,17 +8438,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2019–2020</t>
+          <t>TDF, 3TC, XTC, EFV, NVP, AZT, LPV/r, DTG</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>TDF, 3TC, XTC, EFV, NVP, AZT, LPV/r, DTG</t>
+          <t>2019–2020</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8688,17 +8688,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8713,17 +8713,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>EFV, NVP, AZT, 3TC, TenofovirDF or Abacavir</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8763,17 +8763,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, TenofovirDF or Abacavir</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E334" t="n">
